--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/MARYLAND_2020.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/MARYLAND_2020.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D502"/>
+  <dimension ref="A1:D496"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -391,10 +391,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Asientos</t>
@@ -404,10 +409,15 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>El Llano</t>
@@ -417,10 +427,15 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -448,10 +463,15 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -461,7 +481,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="8">
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -510,10 +535,15 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Acapetahua</t>
@@ -523,10 +553,15 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Catazajá</t>
@@ -562,10 +607,15 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Chenalhó</t>
@@ -588,10 +643,15 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Cintalapa</t>
@@ -601,10 +661,15 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -627,10 +697,15 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Frontera Hidalgo</t>
@@ -653,10 +733,15 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -692,10 +787,15 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -718,10 +823,15 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -731,23 +841,33 @@
         <v>1</v>
       </c>
       <c r="D27">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -757,10 +877,15 @@
         <v>1</v>
       </c>
       <c r="D29">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Metapa</t>
@@ -770,10 +895,15 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -787,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -800,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -809,10 +949,15 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -822,13 +967,18 @@
         <v>1</v>
       </c>
       <c r="D34">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C35">
@@ -839,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Suchiapa</t>
@@ -852,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -865,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -878,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -887,10 +1057,15 @@
         <v>1</v>
       </c>
       <c r="D39">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -904,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -917,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -930,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -939,10 +1129,15 @@
         <v>1</v>
       </c>
       <c r="D43">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -956,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Villaflores</t>
@@ -969,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Total</t>
@@ -996,10 +1201,15 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -1013,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1022,10 +1237,15 @@
         <v>1</v>
       </c>
       <c r="D49">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1035,7 +1255,7 @@
         <v>11</v>
       </c>
       <c r="D50">
-        <v>0.009909909909909909</v>
+        <v>0.009909909909909908</v>
       </c>
     </row>
     <row r="51">
@@ -1053,10 +1273,15 @@
         <v>1</v>
       </c>
       <c r="D51">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -1066,10 +1291,15 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -1079,10 +1309,15 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1098,7 +1333,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1114,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1127,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1140,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1153,19 +1403,29 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1175,10 +1435,15 @@
         <v>10</v>
       </c>
       <c r="D60">
-        <v>0.009009009009009009</v>
+        <v>0.009009009009009007</v>
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1188,10 +1453,15 @@
         <v>10</v>
       </c>
       <c r="D61">
-        <v>0.009009009009009009</v>
+        <v>0.009009009009009007</v>
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1205,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1218,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1231,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1244,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1257,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1284,10 +1579,15 @@
         <v>1</v>
       </c>
       <c r="D68">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1301,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>General Simón Bolívar</t>
@@ -1314,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1323,10 +1633,15 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -1336,10 +1651,15 @@
         <v>1</v>
       </c>
       <c r="D72">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Peñón Blanco</t>
@@ -1349,10 +1669,15 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -1362,10 +1687,15 @@
         <v>1</v>
       </c>
       <c r="D74">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1375,18 +1705,18 @@
         <v>11</v>
       </c>
       <c r="D75">
-        <v>0.009909909909909909</v>
+        <v>0.009909909909909908</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C76">
@@ -1397,19 +1727,29 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Atlautla</t>
@@ -1419,10 +1759,15 @@
         <v>1</v>
       </c>
       <c r="D78">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Capulhuac</t>
@@ -1432,10 +1777,15 @@
         <v>1</v>
       </c>
       <c r="D79">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1449,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1458,10 +1813,15 @@
         <v>1</v>
       </c>
       <c r="D81">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -1475,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C83">
@@ -1488,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Huixquilucan</t>
@@ -1497,10 +1867,15 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -1510,23 +1885,33 @@
         <v>1</v>
       </c>
       <c r="D85">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -1540,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -1553,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Jiquipilco</t>
@@ -1562,10 +1957,15 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Jocotitlán</t>
@@ -1575,10 +1975,15 @@
         <v>1</v>
       </c>
       <c r="D90">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1592,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -1601,13 +2011,18 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C93">
@@ -1618,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1631,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Nicolás Romero</t>
@@ -1640,13 +2065,18 @@
         <v>1</v>
       </c>
       <c r="D95">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C96">
@@ -1657,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1670,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Temascalapa</t>
@@ -1679,10 +2119,15 @@
         <v>1</v>
       </c>
       <c r="D98">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -1692,10 +2137,15 @@
         <v>1</v>
       </c>
       <c r="D99">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Temoaya</t>
@@ -1705,13 +2155,18 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C101">
@@ -1722,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Teoloyucan</t>
@@ -1731,10 +2191,15 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Tepetlaoxtoc</t>
@@ -1744,10 +2209,15 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Tepetlixpa</t>
@@ -1761,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C105">
@@ -1774,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1787,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1802,7 +2287,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -1814,10 +2299,15 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Acámbaro</t>
@@ -1831,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -1844,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C111">
@@ -1857,19 +2357,29 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C112">
         <v>1</v>
       </c>
       <c r="D112">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Atarjea</t>
@@ -1879,10 +2389,15 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1892,10 +2407,15 @@
         <v>11</v>
       </c>
       <c r="D114">
-        <v>0.009909909909909909</v>
+        <v>0.009909909909909908</v>
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -1909,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -1918,13 +2443,18 @@
         <v>1</v>
       </c>
       <c r="D116">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C117">
@@ -1935,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Huanímaro</t>
@@ -1944,10 +2479,15 @@
         <v>1</v>
       </c>
       <c r="D118">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1961,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -1970,10 +2515,15 @@
         <v>1</v>
       </c>
       <c r="D120">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>León</t>
@@ -1983,10 +2533,15 @@
         <v>11</v>
       </c>
       <c r="D121">
-        <v>0.009909909909909909</v>
+        <v>0.009909909909909908</v>
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -2000,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -2013,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -2022,10 +2587,15 @@
         <v>1</v>
       </c>
       <c r="D124">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -2039,19 +2609,29 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>San Diego de la Unión</t>
+          <t>San Diego De La Unión</t>
         </is>
       </c>
       <c r="C126">
         <v>1</v>
       </c>
       <c r="D126">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -2065,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C128">
@@ -2078,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C129">
@@ -2091,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -2100,10 +2695,15 @@
         <v>1</v>
       </c>
       <c r="D130">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -2113,13 +2713,18 @@
         <v>1</v>
       </c>
       <c r="D131">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C132">
@@ -2130,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Xichú</t>
@@ -2139,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="D133">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="134">
@@ -2168,7 +2778,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C135">
@@ -2179,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -2188,39 +2803,54 @@
         <v>1</v>
       </c>
       <c r="D136">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Atlamajalcingo del Monte</t>
+          <t>Atlamajalcingo Del Monte</t>
         </is>
       </c>
       <c r="C137">
         <v>1</v>
       </c>
       <c r="D137">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C138">
         <v>1</v>
       </c>
       <c r="D138">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C139">
@@ -2231,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -2244,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C141">
@@ -2257,9 +2897,14 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C142">
@@ -2270,19 +2915,29 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Coahuayutla de José María Izazaga</t>
+          <t>Coahuayutla De José María Izazaga</t>
         </is>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -2296,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Copala</t>
@@ -2309,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -2322,19 +2987,29 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C147">
         <v>1</v>
       </c>
       <c r="D147">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Cuautepec</t>
@@ -2344,23 +3019,33 @@
         <v>1</v>
       </c>
       <c r="D148">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cuetzala del Progreso</t>
+          <t>Cuetzala Del Progreso</t>
         </is>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
       <c r="D149">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -2370,13 +3055,18 @@
         <v>1</v>
       </c>
       <c r="D150">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C151">
@@ -2387,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -2396,13 +3091,18 @@
         <v>1</v>
       </c>
       <c r="D152">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C153">
@@ -2413,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -2422,10 +3127,15 @@
         <v>1</v>
       </c>
       <c r="D154">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -2439,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -2448,10 +3163,15 @@
         <v>1</v>
       </c>
       <c r="D156">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -2461,10 +3181,15 @@
         <v>1</v>
       </c>
       <c r="D157">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -2478,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -2491,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -2504,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -2513,10 +3253,15 @@
         <v>1</v>
       </c>
       <c r="D161">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -2526,23 +3271,33 @@
         <v>1</v>
       </c>
       <c r="D162">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -2556,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Tetipac</t>
@@ -2565,10 +3325,15 @@
         <v>1</v>
       </c>
       <c r="D165">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -2578,26 +3343,36 @@
         <v>1</v>
       </c>
       <c r="D166">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tlalixtaquilla de Maldonado</t>
+          <t>Tlalixtaquilla De Maldonado</t>
         </is>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="D167">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C168">
@@ -2608,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -2621,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Zapotitlán Tablas</t>
@@ -2630,10 +3415,15 @@
         <v>1</v>
       </c>
       <c r="D170">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -2643,10 +3433,15 @@
         <v>1</v>
       </c>
       <c r="D171">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2674,10 +3469,15 @@
         <v>1</v>
       </c>
       <c r="D173">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Calnali</t>
@@ -2691,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Cardonal</t>
@@ -2700,10 +3505,15 @@
         <v>1</v>
       </c>
       <c r="D175">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -2717,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Huazalingo</t>
@@ -2726,13 +3541,18 @@
         <v>1</v>
       </c>
       <c r="D177">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Huejutla de Reyes</t>
+          <t>Huejutla De Reyes</t>
         </is>
       </c>
       <c r="C178">
@@ -2743,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -2756,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -2769,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -2782,35 +3617,50 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mixquiahuala de Juárez</t>
+          <t>Mixquiahuala De Juárez</t>
         </is>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Molango de Escamilla</t>
+          <t>Molango De Escamilla</t>
         </is>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C184">
@@ -2821,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Pisaflores</t>
@@ -2834,19 +3689,29 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
       <c r="D186">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>San Agustín Tlaxiaca</t>
@@ -2856,10 +3721,15 @@
         <v>1</v>
       </c>
       <c r="D187">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Tasquillo</t>
@@ -2869,10 +3739,15 @@
         <v>1</v>
       </c>
       <c r="D188">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -2882,10 +3757,15 @@
         <v>1</v>
       </c>
       <c r="D189">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Tepetitlán</t>
@@ -2895,10 +3775,15 @@
         <v>1</v>
       </c>
       <c r="D190">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Tianguistengo</t>
@@ -2908,10 +3793,15 @@
         <v>1</v>
       </c>
       <c r="D191">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Tlanchinol</t>
@@ -2921,13 +3811,18 @@
         <v>1</v>
       </c>
       <c r="D192">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C193">
@@ -2938,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Xochicoatlán</t>
@@ -2947,13 +3847,18 @@
         <v>1</v>
       </c>
       <c r="D194">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Zacualtipán de Ángeles</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C195">
@@ -2964,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -2973,10 +3883,15 @@
         <v>1</v>
       </c>
       <c r="D196">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3004,10 +3919,15 @@
         <v>1</v>
       </c>
       <c r="D198">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -3017,10 +3937,15 @@
         <v>1</v>
       </c>
       <c r="D199">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -3030,13 +3955,18 @@
         <v>1</v>
       </c>
       <c r="D200">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C201">
@@ -3047,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -3060,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -3069,23 +4009,33 @@
         <v>1</v>
       </c>
       <c r="D203">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -3099,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -3112,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Tototlán</t>
@@ -3121,10 +4081,15 @@
         <v>1</v>
       </c>
       <c r="D207">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -3134,10 +4099,15 @@
         <v>1</v>
       </c>
       <c r="D208">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -3147,10 +4117,15 @@
         <v>1</v>
       </c>
       <c r="D209">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3178,10 +4153,15 @@
         <v>1</v>
       </c>
       <c r="D211">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -3195,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Aquila</t>
@@ -3204,10 +4189,15 @@
         <v>1</v>
       </c>
       <c r="D213">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -3221,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Erongarícuaro</t>
@@ -3230,10 +4225,15 @@
         <v>1</v>
       </c>
       <c r="D215">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -3247,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Huaniqueo</t>
@@ -3256,10 +4261,15 @@
         <v>1</v>
       </c>
       <c r="D217">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -3273,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -3286,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -3299,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -3308,10 +4333,15 @@
         <v>1</v>
       </c>
       <c r="D221">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -3321,10 +4351,15 @@
         <v>1</v>
       </c>
       <c r="D222">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -3338,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -3351,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -3360,10 +4405,15 @@
         <v>1</v>
       </c>
       <c r="D225">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -3377,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3408,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -3421,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -3434,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -3447,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -3460,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -3469,13 +4549,18 @@
         <v>1</v>
       </c>
       <c r="D233">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C234">
@@ -3486,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -3499,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -3512,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Yecapixtla</t>
@@ -3525,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Zacualpan de Amilpas</t>
+          <t>Zacualpan De Amilpas</t>
         </is>
       </c>
       <c r="C238">
@@ -3538,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3565,10 +4675,15 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -3578,10 +4693,15 @@
         <v>1</v>
       </c>
       <c r="D241">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3609,10 +4729,15 @@
         <v>1</v>
       </c>
       <c r="D243">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>General Zaragoza</t>
@@ -3622,10 +4747,15 @@
         <v>1</v>
       </c>
       <c r="D244">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -3639,19 +4769,29 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3679,10 +4819,15 @@
         <v>1</v>
       </c>
       <c r="D248">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Ayotzintepec</t>
@@ -3696,9 +4841,14 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Fresnillo de Trujano</t>
+          <t>Fresnillo De Trujano</t>
         </is>
       </c>
       <c r="C250">
@@ -3709,35 +4859,50 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C253">
@@ -3748,32 +4913,47 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Mariscala de Juárez</t>
+          <t>Mariscala De Juárez</t>
         </is>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Natividad</t>
@@ -3783,13 +4963,18 @@
         <v>1</v>
       </c>
       <c r="D256">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C257">
@@ -3800,35 +4985,50 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Pinotepa de Don Luis</t>
+          <t>Pinotepa De Don Luis</t>
         </is>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerero</t>
+          <t>Putla Villa De Guerero</t>
         </is>
       </c>
       <c r="C260">
@@ -3839,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -3848,10 +5053,15 @@
         <v>1</v>
       </c>
       <c r="D261">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>San Agustín Chayuco</t>
@@ -3865,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>San Agustín Loxicha</t>
@@ -3874,10 +5089,15 @@
         <v>1</v>
       </c>
       <c r="D263">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>San Agustín Yatareni</t>
@@ -3887,10 +5107,15 @@
         <v>1</v>
       </c>
       <c r="D264">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>San Andrés Huaxpaltepec</t>
@@ -3904,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>San Andrés Solaga</t>
@@ -3913,10 +5143,15 @@
         <v>1</v>
       </c>
       <c r="D266">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -3926,23 +5161,33 @@
         <v>1</v>
       </c>
       <c r="D267">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>San Francisco del Mar</t>
+          <t>San Francisco Del Mar</t>
         </is>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>San Francisco Telixtlahuaca</t>
@@ -3952,10 +5197,15 @@
         <v>1</v>
       </c>
       <c r="D269">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>San Juan Bautista Coixtlahuaca</t>
@@ -3965,10 +5215,15 @@
         <v>1</v>
       </c>
       <c r="D270">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>San Juan Bautista Valle Nacional</t>
@@ -3982,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>San Juan Lachao</t>
@@ -3991,10 +5251,15 @@
         <v>1</v>
       </c>
       <c r="D272">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>San Juan Lachigalla</t>
@@ -4004,10 +5269,15 @@
         <v>1</v>
       </c>
       <c r="D273">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>San Juan Mazatlán</t>
@@ -4021,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>San Juan Ozolotepec</t>
@@ -4030,10 +5305,15 @@
         <v>1</v>
       </c>
       <c r="D275">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>San Juan Quiotepec</t>
@@ -4043,10 +5323,15 @@
         <v>1</v>
       </c>
       <c r="D276">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>San Lorenzo</t>
@@ -4060,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>San Lucas Ojitlán</t>
@@ -4069,10 +5359,15 @@
         <v>1</v>
       </c>
       <c r="D278">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>San Luis Amatlán</t>
@@ -4082,10 +5377,15 @@
         <v>1</v>
       </c>
       <c r="D279">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>San Martín Itunyoso</t>
@@ -4095,10 +5395,15 @@
         <v>1</v>
       </c>
       <c r="D280">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -4108,10 +5413,15 @@
         <v>1</v>
       </c>
       <c r="D281">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>San Miguel Aloápam</t>
@@ -4125,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>San Miguel Amatitlán</t>
@@ -4134,10 +5449,15 @@
         <v>1</v>
       </c>
       <c r="D283">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>San Miguel Tlacamama</t>
@@ -4151,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>San Miguel Tlacotepec</t>
@@ -4164,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>San Nicolás</t>
@@ -4173,10 +5503,15 @@
         <v>1</v>
       </c>
       <c r="D286">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>San Nicolás Hidalgo</t>
@@ -4190,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>San Pedro Huamelula</t>
@@ -4203,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>San Sebastián Ixcapa</t>
@@ -4212,10 +5557,15 @@
         <v>1</v>
       </c>
       <c r="D289">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -4229,9 +5579,14 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Santa Inés del Monte</t>
+          <t>Santa Inés Del Monte</t>
         </is>
       </c>
       <c r="C291">
@@ -4242,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Santa Inés Yatzeche</t>
@@ -4255,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Santa María del Tule</t>
+          <t>Santa María Del Tule</t>
         </is>
       </c>
       <c r="C293">
@@ -4268,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Santa María Ecatepec</t>
@@ -4277,10 +5647,15 @@
         <v>1</v>
       </c>
       <c r="D294">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Santa María Huatulco</t>
@@ -4290,10 +5665,15 @@
         <v>1</v>
       </c>
       <c r="D295">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Santa María Huazolotitlán</t>
@@ -4303,10 +5683,15 @@
         <v>1</v>
       </c>
       <c r="D296">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Santa María Ipalapa</t>
@@ -4320,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Santa María Lachixío</t>
@@ -4333,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Santa María Mixtequilla</t>
@@ -4342,10 +5737,15 @@
         <v>1</v>
       </c>
       <c r="D299">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Santa María Zacatepec</t>
@@ -4359,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Santiago Apoala</t>
@@ -4368,10 +5773,15 @@
         <v>1</v>
       </c>
       <c r="D301">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Santiago Camotlán</t>
@@ -4381,10 +5791,15 @@
         <v>1</v>
       </c>
       <c r="D302">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Santiago Ixtayutla</t>
@@ -4394,10 +5809,15 @@
         <v>1</v>
       </c>
       <c r="D303">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -4407,10 +5827,15 @@
         <v>10</v>
       </c>
       <c r="D304">
-        <v>0.009009009009009009</v>
+        <v>0.009009009009009007</v>
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -4420,10 +5845,15 @@
         <v>1</v>
       </c>
       <c r="D305">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -4433,10 +5863,15 @@
         <v>1</v>
       </c>
       <c r="D306">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Santiago Niltepec</t>
@@ -4446,10 +5881,15 @@
         <v>1</v>
       </c>
       <c r="D307">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Santiago Tetepec</t>
@@ -4459,10 +5899,15 @@
         <v>1</v>
       </c>
       <c r="D308">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Santo Domingo Nuxaá</t>
@@ -4472,10 +5917,15 @@
         <v>1</v>
       </c>
       <c r="D309">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -4489,9 +5939,14 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Tanetze de Zaragoza</t>
+          <t>Tanetze De Zaragoza</t>
         </is>
       </c>
       <c r="C311">
@@ -4502,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4533,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -4546,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Acatzingo</t>
@@ -4555,10 +6025,15 @@
         <v>1</v>
       </c>
       <c r="D315">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Ahuacatlán</t>
@@ -4568,10 +6043,15 @@
         <v>1</v>
       </c>
       <c r="D316">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Ahuatlán</t>
@@ -4581,10 +6061,15 @@
         <v>1</v>
       </c>
       <c r="D317">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Ajalpan</t>
@@ -4594,10 +6079,15 @@
         <v>1</v>
       </c>
       <c r="D318">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -4611,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Calpan</t>
@@ -4620,10 +6115,15 @@
         <v>1</v>
       </c>
       <c r="D320">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -4637,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -4646,10 +6151,15 @@
         <v>1</v>
       </c>
       <c r="D322">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -4659,10 +6169,15 @@
         <v>1</v>
       </c>
       <c r="D323">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -4676,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Chilchotla</t>
@@ -4685,10 +6205,15 @@
         <v>1</v>
       </c>
       <c r="D325">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -4702,19 +6227,29 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C327">
         <v>1</v>
       </c>
       <c r="D327">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Domingo Arenas</t>
@@ -4724,10 +6259,15 @@
         <v>1</v>
       </c>
       <c r="D328">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -4741,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -4750,10 +6295,15 @@
         <v>1</v>
       </c>
       <c r="D330">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -4767,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -4776,10 +6331,15 @@
         <v>1</v>
       </c>
       <c r="D332">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -4793,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Hueytamalco</t>
@@ -4802,23 +6367,33 @@
         <v>1</v>
       </c>
       <c r="D334">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Ixcamilpa de Guerero</t>
+          <t>Ixcamilpa De Guerero</t>
         </is>
       </c>
       <c r="C335">
         <v>1</v>
       </c>
       <c r="D335">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -4828,13 +6403,18 @@
         <v>1</v>
       </c>
       <c r="D336">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C337">
@@ -4845,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Jopala</t>
@@ -4858,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Juan C. Bonilla</t>
@@ -4867,23 +6457,33 @@
         <v>1</v>
       </c>
       <c r="D339">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C340">
         <v>1</v>
       </c>
       <c r="D340">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Nealtican</t>
@@ -4897,6 +6497,11 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
           <t>Pahuatlán</t>
@@ -4906,23 +6511,33 @@
         <v>1</v>
       </c>
       <c r="D342">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C343">
         <v>1</v>
       </c>
       <c r="D343">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>Petlalcingo</t>
@@ -4932,10 +6547,15 @@
         <v>1</v>
       </c>
       <c r="D344">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -4945,10 +6565,15 @@
         <v>1</v>
       </c>
       <c r="D345">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -4962,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -4975,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>San Gregorio Atzompa</t>
@@ -4984,10 +6619,15 @@
         <v>1</v>
       </c>
       <c r="D348">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>San Pablo Anicano</t>
@@ -5001,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -5010,10 +6655,15 @@
         <v>1</v>
       </c>
       <c r="D350">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>San Pedro Yeloixtlahuaca</t>
@@ -5027,19 +6677,29 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>San Salvador el Verde</t>
+          <t>San Salvador El Verde</t>
         </is>
       </c>
       <c r="C352">
         <v>1</v>
       </c>
       <c r="D352">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
           <t>Santa Inés Ahuatempan</t>
@@ -5053,6 +6713,11 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
           <t>Santa Isabel Cholula</t>
@@ -5062,10 +6727,15 @@
         <v>1</v>
       </c>
       <c r="D354">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -5079,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -5092,6 +6767,11 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -5105,9 +6785,14 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Tepanco de López</t>
+          <t>Tepanco De López</t>
         </is>
       </c>
       <c r="C358">
@@ -5118,9 +6803,14 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Tepatlaxco de Hidalgo</t>
+          <t>Tepatlaxco De Hidalgo</t>
         </is>
       </c>
       <c r="C359">
@@ -5131,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -5140,10 +6835,15 @@
         <v>1</v>
       </c>
       <c r="D360">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Tepetzintla</t>
@@ -5153,13 +6853,18 @@
         <v>1</v>
       </c>
       <c r="D361">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C362">
@@ -5170,9 +6875,14 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C363">
@@ -5183,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Tlapanalá</t>
@@ -5192,10 +6907,15 @@
         <v>1</v>
       </c>
       <c r="D364">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Tochimilco</t>
@@ -5205,10 +6925,15 @@
         <v>1</v>
       </c>
       <c r="D365">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>Vicente Guerero</t>
@@ -5222,19 +6947,29 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Xayacatlán de Bravo</t>
+          <t>Xayacatlán De Bravo</t>
         </is>
       </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -5248,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -5257,10 +6997,15 @@
         <v>1</v>
       </c>
       <c r="D369">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -5274,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5305,6 +7055,11 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
           <t>Colón</t>
@@ -5314,26 +7069,36 @@
         <v>1</v>
       </c>
       <c r="D373">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C374">
         <v>1</v>
       </c>
       <c r="D374">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C375">
@@ -5344,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -5357,19 +7127,29 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C377">
         <v>1</v>
       </c>
       <c r="D377">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5397,10 +7177,15 @@
         <v>1</v>
       </c>
       <c r="D379">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
           <t>Cerritos</t>
@@ -5414,19 +7199,29 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C381">
         <v>1</v>
       </c>
       <c r="D381">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>Guadalcázar</t>
@@ -5436,10 +7231,15 @@
         <v>1</v>
       </c>
       <c r="D382">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -5453,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -5462,10 +7267,15 @@
         <v>1</v>
       </c>
       <c r="D384">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -5479,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -5488,10 +7303,15 @@
         <v>1</v>
       </c>
       <c r="D386">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -5505,6 +7325,11 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -5514,49 +7339,69 @@
         <v>1</v>
       </c>
       <c r="D388">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Tanquián de Escobedo</t>
+          <t>Tanquián De Escobedo</t>
         </is>
       </c>
       <c r="C389">
         <v>1</v>
       </c>
       <c r="D389">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Villa de Guadalupe</t>
+          <t>Villa De Guadalupe</t>
         </is>
       </c>
       <c r="C390">
         <v>1</v>
       </c>
       <c r="D390">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C391">
         <v>1</v>
       </c>
       <c r="D391">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -5566,10 +7411,15 @@
         <v>1</v>
       </c>
       <c r="D392">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -5579,10 +7429,15 @@
         <v>1</v>
       </c>
       <c r="D393">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5614,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Escuinapa</t>
@@ -5623,10 +7483,15 @@
         <v>1</v>
       </c>
       <c r="D396">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -5640,6 +7505,11 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5667,10 +7537,15 @@
         <v>1</v>
       </c>
       <c r="D399">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -5680,10 +7555,15 @@
         <v>1</v>
       </c>
       <c r="D400">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5715,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -5724,10 +7609,15 @@
         <v>1</v>
       </c>
       <c r="D403">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Comalcalco</t>
@@ -5737,10 +7627,15 @@
         <v>1</v>
       </c>
       <c r="D404">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -5754,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>Paraíso</t>
@@ -5763,10 +7663,15 @@
         <v>1</v>
       </c>
       <c r="D406">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5794,10 +7699,15 @@
         <v>1</v>
       </c>
       <c r="D408">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>Antiguo Morelos</t>
@@ -5807,10 +7717,15 @@
         <v>1</v>
       </c>
       <c r="D409">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -5820,10 +7735,15 @@
         <v>1</v>
       </c>
       <c r="D410">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -5837,6 +7757,11 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -5846,10 +7771,15 @@
         <v>1</v>
       </c>
       <c r="D412">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>Tula</t>
@@ -5859,10 +7789,15 @@
         <v>1</v>
       </c>
       <c r="D413">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -5876,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5907,19 +7847,29 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Ixtacuixtla de Mariano Matamoros</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C417">
         <v>1</v>
       </c>
       <c r="D417">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -5933,19 +7883,29 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>San Pablo del Monte</t>
+          <t>San Pablo Del Monte</t>
         </is>
       </c>
       <c r="C419">
         <v>1</v>
       </c>
       <c r="D419">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Santa Cruz Tlaxcala</t>
@@ -5955,10 +7915,15 @@
         <v>1</v>
       </c>
       <c r="D420">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Terrenate</t>
@@ -5968,10 +7933,15 @@
         <v>1</v>
       </c>
       <c r="D421">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -5985,6 +7955,11 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>Tocatlán</t>
@@ -5994,10 +7969,15 @@
         <v>1</v>
       </c>
       <c r="D423">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -6007,10 +7987,15 @@
         <v>1</v>
       </c>
       <c r="D424">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6042,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>Amatitlán</t>
@@ -6051,10 +8041,15 @@
         <v>1</v>
       </c>
       <c r="D427">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -6064,10 +8059,15 @@
         <v>1</v>
       </c>
       <c r="D428">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Atoyac</t>
@@ -6077,10 +8077,15 @@
         <v>1</v>
       </c>
       <c r="D429">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -6094,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>Carrillo Puerto</t>
@@ -6103,10 +8113,15 @@
         <v>1</v>
       </c>
       <c r="D431">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -6120,19 +8135,29 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Cazones de Herrera</t>
+          <t>Cazones De Herrera</t>
         </is>
       </c>
       <c r="C433">
         <v>1</v>
       </c>
       <c r="D433">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Chiconquiaco</t>
@@ -6146,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -6159,6 +8189,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -6172,9 +8207,14 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C437">
@@ -6185,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>Cuichapa</t>
@@ -6194,10 +8239,15 @@
         <v>1</v>
       </c>
       <c r="D438">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -6207,10 +8257,15 @@
         <v>1</v>
       </c>
       <c r="D439">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>El Higo</t>
@@ -6220,10 +8275,15 @@
         <v>1</v>
       </c>
       <c r="D440">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -6237,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -6246,10 +8311,15 @@
         <v>1</v>
       </c>
       <c r="D442">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -6259,23 +8329,33 @@
         <v>1</v>
       </c>
       <c r="D443">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C444">
         <v>1</v>
       </c>
       <c r="D444">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -6285,23 +8365,33 @@
         <v>1</v>
       </c>
       <c r="D445">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Ixhuatlán de Madero</t>
+          <t>Ixhuatlán De Madero</t>
         </is>
       </c>
       <c r="C446">
         <v>1</v>
       </c>
       <c r="D446">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -6315,6 +8405,11 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -6324,10 +8419,15 @@
         <v>1</v>
       </c>
       <c r="D448">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Juan Rodríguez Clara</t>
@@ -6337,10 +8437,15 @@
         <v>1</v>
       </c>
       <c r="D449">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -6354,9 +8459,14 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C451">
@@ -6367,6 +8477,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Miahuatlán</t>
@@ -6376,10 +8491,15 @@
         <v>1</v>
       </c>
       <c r="D452">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -6393,6 +8513,11 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -6402,10 +8527,15 @@
         <v>1</v>
       </c>
       <c r="D454">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -6419,6 +8549,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -6428,23 +8563,33 @@
         <v>1</v>
       </c>
       <c r="D456">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Paso de Ovejas</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C457">
         <v>1</v>
       </c>
       <c r="D457">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Perote</t>
@@ -6454,10 +8599,15 @@
         <v>1</v>
       </c>
       <c r="D458">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -6471,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Puente Nacional</t>
@@ -6480,10 +8635,15 @@
         <v>1</v>
       </c>
       <c r="D460">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -6497,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -6506,10 +8671,15 @@
         <v>1</v>
       </c>
       <c r="D462">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -6519,23 +8689,33 @@
         <v>1</v>
       </c>
       <c r="D463">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Sayula de Alemán</t>
+          <t>Sayula De Alemán</t>
         </is>
       </c>
       <c r="C464">
         <v>1</v>
       </c>
       <c r="D464">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
           <t>Soledad Atzompa</t>
@@ -6545,10 +8725,15 @@
         <v>1</v>
       </c>
       <c r="D465">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
           <t>Tantoyuca</t>
@@ -6558,10 +8743,15 @@
         <v>1</v>
       </c>
       <c r="D466">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -6571,10 +8761,15 @@
         <v>1</v>
       </c>
       <c r="D467">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>Tenampa</t>
@@ -6584,10 +8779,15 @@
         <v>1</v>
       </c>
       <c r="D468">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Tepatlaxco</t>
@@ -6597,10 +8797,15 @@
         <v>1</v>
       </c>
       <c r="D469">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -6610,10 +8815,15 @@
         <v>1</v>
       </c>
       <c r="D470">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -6627,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Tlachichilco</t>
@@ -6636,13 +8851,18 @@
         <v>1</v>
       </c>
       <c r="D472">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Tlacotepec de Mejía</t>
+          <t>Tlacotepec De Mejía</t>
         </is>
       </c>
       <c r="C473">
@@ -6653,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -6662,10 +8887,15 @@
         <v>1</v>
       </c>
       <c r="D474">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Tonayán</t>
@@ -6675,10 +8905,15 @@
         <v>1</v>
       </c>
       <c r="D475">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -6692,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -6701,10 +8941,15 @@
         <v>1</v>
       </c>
       <c r="D477">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -6718,6 +8963,11 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -6727,10 +8977,15 @@
         <v>1</v>
       </c>
       <c r="D479">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Xico</t>
@@ -6740,10 +8995,15 @@
         <v>1</v>
       </c>
       <c r="D480">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -6757,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Zentla</t>
@@ -6766,10 +9031,15 @@
         <v>1</v>
       </c>
       <c r="D482">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -6779,23 +9049,33 @@
         <v>1</v>
       </c>
       <c r="D483">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Zontecomatlán de López y Fuentes</t>
+          <t>Zontecomatlán De López Y Fuentes</t>
         </is>
       </c>
       <c r="C484">
         <v>1</v>
       </c>
       <c r="D484">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6823,10 +9103,15 @@
         <v>1</v>
       </c>
       <c r="D486">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6836,7 +9121,7 @@
         <v>1</v>
       </c>
       <c r="D487">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="488">
@@ -6858,6 +9143,11 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
           <t>Loreto</t>
@@ -6867,10 +9157,15 @@
         <v>1</v>
       </c>
       <c r="D489">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -6880,10 +9175,15 @@
         <v>1</v>
       </c>
       <c r="D490">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -6893,10 +9193,15 @@
         <v>1</v>
       </c>
       <c r="D491">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>Tabasco</t>
@@ -6906,10 +9211,15 @@
         <v>1</v>
       </c>
       <c r="D492">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>Villa García</t>
@@ -6919,10 +9229,15 @@
         <v>1</v>
       </c>
       <c r="D493">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -6932,10 +9247,15 @@
         <v>1</v>
       </c>
       <c r="D494">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6959,41 +9279,6 @@
       </c>
       <c r="D496">
         <v>1</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 497,795</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>Octubre de 2021</t>
-        </is>
       </c>
     </row>
   </sheetData>
